--- a/archive/2026/2026-10-29.xlsx
+++ b/archive/2026/2026-10-29.xlsx
@@ -11160,22 +11160,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>00795B</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中信美國公債20年</t>
+          <t>緯致</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>368</v>
       </c>
       <c r="E27" t="n">
-        <v>26.39</v>
+        <v>129</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.12</v>
+        <v>1.5</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -11206,22 +11206,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>00795B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>緯致</t>
+          <t>中信美國公債20年</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
         <v>368</v>
       </c>
       <c r="E28" t="n">
-        <v>129</v>
+        <v>26.39</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.5</v>
+        <v>0.12</v>
       </c>
       <c r="H28" t="n">
         <v>25</v>
